--- a/stories/arbres/ATOM-TMP.SEM.002-01.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam prépare son cartable avec papa. Papa dit : demain c'est lundi. Lundi, mardi, jeudi, vendredi : Adam va à l'école. Mercredi, Adam reste à la maison. Il joue avec papa. Samedi, Adam reste aussi à la maison. Dimanche encore. Papa dit : samedi et dimanche, c'est le week-end. Adam range le cartable mercredi. Pas d'école ce jour-là. Il dessine. Papa dit : mercredi, samedi, dimanche, on est à la maison.</t>
+          <t>Adam prépare son cartable avec papa. Demain c'est lundi. Lundi, mardi, jeudi, vendredi : Adam va à l'école. Mercredi, Adam reste à la maison. Il joue avec papa. Samedi, Adam reste aussi à la maison. Dimanche encore. Samedi et dimanche, c'est le week-end. Adam range le cartable mercredi. Pas d'école ce jour-là. Il dessine. Mercredi, samedi, dimanche, on est à la maison.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Adam prépare son cartable avec papa.
+papa|Demain c'est lundi. Lundi, mardi, jeudi, vendredi : Adam va à l'école. Mercredi, Adam reste à la maison. Il joue avec papa. Samedi, Adam reste aussi à la maison. Dimanche encore.
+papa|Samedi et dimanche, c'est le week-end.
+narrateur|Adam range le cartable mercredi. Pas d'école ce jour-là. Il dessine.
+papa|Mercredi, samedi, dimanche, on est à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Adam est à la maison le mercredi. Quels autres jours aussi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a nommé mercredi. Il a nommé samedi et dimanche. C'est le week-end.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Adam range ses crayons. Papa prépare le goûter.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.002-01.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 papa|Mercredi, samedi, dimanche, on est à la maison.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Adam est à la maison le mercredi. Quels autres jours aussi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Adam a nommé mercredi. Il a nommé samedi et dimanche. C'est le week-end.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Adam range ses crayons. Papa prépare le goûter.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.SEM.002-01.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le mercredi d'Adam</t>
+          <t>Une tache sur le soleil</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah veut un soleil jaune à la fenêtre. Mercredi, le pinceau trop chargé fait une tache. Ils essuient. Samedi le soleil sèche. Dimanche, week-end, il chauffe la vitre.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam prépare son cartable avec papa. Demain c'est lundi. Lundi, mardi, jeudi, vendredi : Adam va à l'école. Mercredi, Adam reste à la maison. Il joue avec papa. Samedi, Adam reste aussi à la maison. Dimanche encore. Samedi et dimanche, c'est le week-end. Adam range le cartable mercredi. Pas d'école ce jour-là. Il dessine. Mercredi, samedi, dimanche, on est à la maison.</t>
+          <t>Sur la table, un pot de bleu tremble. La lumière passe dans l'eau du pot. Ça sent la peinture, un peu sucré. C'est mercredi, Sarah. Pas de cartable. On reste ? Oui. Mercredi, on reste. On peint ? Tu veux un soleil ? Un grand soleil jaune. Papa pose une grande feuille. Le papier est un peu rêche. Un coin se soulève. Sarah le plaque avec la main. Tu le tiens bien. En ce moment, Sarah trempe le pinceau. Le jaune est épais, comme du miel. Elle pose un rond au milieu. Le soleil commence. Il est chaud déjà ? Presque. Elle veut un rayon. Le pinceau va vers le bleu. Le bleu est trop chargé. Une goutte tombe. Elle fait une tache sur le jaune. Oh. Le soleil a une tache. Le pinceau avait trop de bleu. On essuie ? Oui. Sarah prend le linge près du pot. Le linge est doux, un peu rêche. Elle tapote la tache. Le bleu pâlit. Tu essuies tout doux. Merci. Le jaune revient. Un peu. On laisse sécher. Quand on le verra ? Samedi, on regardera. Dimanche, on le mettra à la fenêtre. Samedi et dimanche, c'est le week-end. Pas d'école. Pas d'école. Comme mercredi. Sarah pose le pinceau sur le bord. Une petite tache bleue reste au coin. Le soleil attend sur la table. Il sèche, là. J'attends samedi. Papa rince le pinceau. L'eau devient verte, puis claire. Le bleu s'en va. Oui. Comme la tache. La feuille tremble un peu. Sarah pose une tasse dessus. Pour le coin. Il ne vole plus. Mercredi, on a peint. Le week-end, on accrochera.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam prépare son cartable avec papa. Papa dit : demain c'est lundi. Lundi, mardi, jeudi, vendredi : Adam va à l'école. &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;, Adam reste à la maison. Il joue avec papa. Samedi, Adam reste aussi à la maison. Dimanche encore. Papa dit : samedi et dimanche, c'est le week-end. Adam range le cartable mercredi. Pas d'école ce jour-là. Il dessine. Papa dit : mercredi, samedi, dimanche, on est à la maison.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sur la table, un pot de bleu tremble. La lumière passe dans l'eau du pot. Ça sent la peinture, un peu sucré. C'est mercredi, Sarah. Pas de cartable. On reste ? Oui. Mercredi, on reste. On peint ? Tu veux un soleil ? Un grand soleil jaune. Papa pose une grande feuille. Le papier est un peu rêche. Un coin se soulève. Sarah le plaque avec la main. Tu le tiens bien. En ce moment, Sarah trempe le pinceau. Le jaune est épais, comme du miel. Elle pose un rond au milieu. Le soleil commence. Il est chaud déjà ? Presque. Elle veut un rayon. Le pinceau va vers le bleu. Le bleu est trop chargé. Une goutte tombe. Elle fait une tache sur le jaune. Oh. Le soleil a une tache. Le pinceau avait trop de bleu. On essuie ? Oui. Sarah prend le linge près du pot. Le linge est doux, un peu rêche. Elle tapote la tache. Le bleu pâlit. Tu essuies tout doux. Merci. Le jaune revient. Un peu. On laisse sécher. Quand on le verra ? Samedi, on regardera. Dimanche, on le mettra à la fenêtre. Samedi et dimanche, c'est le week-end. Pas d'école. Pas d'école. Comme mercredi. Sarah pose le pinceau sur le bord. Une petite tache bleue reste au coin. Le soleil attend sur la table. Il sèche, là. J'attends samedi. Papa rince le pinceau. L'eau devient verte, puis claire. Le bleu s'en va. Oui. Comme la tache. La feuille tremble un peu. Sarah pose une tasse dessus. Pour le coin. Il ne vole plus. Mercredi, on a peint. Le week-end, on accrochera.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,72 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Adam prépare son cartable avec papa.
-papa|Demain c'est lundi. Lundi, mardi, jeudi, vendredi : Adam va à l'école. Mercredi, Adam reste à la maison. Il joue avec papa. Samedi, Adam reste aussi à la maison. Dimanche encore.
+          <t>narrateur|Sur la table, un pot de bleu tremble.
+narrateur|La lumière passe dans l'eau du pot.
+narrateur|Ça sent la peinture, un peu sucré.
+papa|C'est mercredi, Sarah.
+papa|Pas de cartable.
+enfant-f|On reste ?
+papa|Oui.
+papa|Mercredi, on reste.
+enfant-f|On peint ?
+papa|Tu veux un soleil ?
+enfant-f|Un grand soleil jaune.
+narrateur|Papa pose une grande feuille.
+narrateur|Le papier est un peu rêche.
+narrateur|Un coin se soulève.
+narrateur|Sarah le plaque avec la main.
+papa|Tu le tiens bien.
+narrateur|En ce moment, Sarah trempe le pinceau.
+narrateur|Le jaune est épais, comme du miel.
+narrateur|Elle pose un rond au milieu.
+enfant-f|Le soleil commence.
+papa|Il est chaud déjà ?
+enfant-f|Presque.
+narrateur|Elle veut un rayon.
+narrateur|Le pinceau va vers le bleu.
+narrateur|Le bleu est trop chargé.
+narrateur|Une goutte tombe.
+narrateur|Elle fait une tache sur le jaune.
+enfant-f|Oh.
+enfant-f|Le soleil a une tache.
+papa|Le pinceau avait trop de bleu.
+papa|On essuie ?
+enfant-f|Oui.
+narrateur|Sarah prend le linge près du pot.
+narrateur|Le linge est doux, un peu rêche.
+narrateur|Elle tapote la tache.
+narrateur|Le bleu pâlit.
+papa|Tu essuies tout doux.
+papa|Merci.
+enfant-f|Le jaune revient.
+papa|Un peu.
+papa|On laisse sécher.
+enfant-f|Quand on le verra ?
+papa|Samedi, on regardera.
+papa|Dimanche, on le mettra à la fenêtre.
 papa|Samedi et dimanche, c'est le week-end.
-narrateur|Adam range le cartable mercredi. Pas d'école ce jour-là. Il dessine.
-papa|Mercredi, samedi, dimanche, on est à la maison.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-f|Pas d'école.
+papa|Pas d'école.
+papa|Comme mercredi.
+narrateur|Sarah pose le pinceau sur le bord.
+narrateur|Une petite tache bleue reste au coin.
+narrateur|Le soleil attend sur la table.
+papa|Il sèche, là.
+enfant-f|J'attends samedi.
+narrateur|Papa rince le pinceau.
+narrateur|L'eau devient verte, puis claire.
+enfant-f|Le bleu s'en va.
+papa|Oui.
+papa|Comme la tache.
+narrateur|La feuille tremble un peu.
+narrateur|Sarah pose une tasse dessus.
+papa|Pour le coin.
+enfant-f|Il ne vole plus.
+papa|Mercredi, on a peint.
+papa|Le week-end, on accrochera.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,12 +1414,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Adam est à la maison le mercredi. Quels autres jours aussi ?</t>
+          <t>Quels autres jours, comme mercredi, sans l'école ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Adam est à la maison le &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;. Quels autres jours aussi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Quels autres jours, comme mercredi, sans l'école ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1364,7 +1434,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>week-end | weekend | samedi | dimanche | le week-end</t>
+          <t>week-end | weekend | samedi | dimanche | le week-end | mercredi</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1428,7 +1498,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1504,10 +1574,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Adam est à la maison le mercredi. Quels autres jours aussi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Quels autres jours, comme mercredi, sans l'école ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,12 +1601,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Adam a nommé mercredi. Il a nommé samedi et dimanche. C'est le week-end.</t>
+          <t>Sarah touche le papier du doigt. Le jaune n'est plus collant. Samedi. Et dimanche. Oui. C'est le week-end. Comme mercredi, pas d'école. On accroche ? Dimanche, à la fenêtre. Sarah souffle un peu sur le rond. Le papier ne bouge plus. Il est prêt. Le bleu a disparu. Tu as essuyé. Bravo. Une lueur passe sur le jaune. Tu vois le rayon ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam a nommé &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;. Il a nommé samedi et dimanche. C'est le week-end.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah touche le papier du doigt. Le jaune n'est plus collant. Samedi. Et dimanche. Oui. C'est le week-end. Comme mercredi, pas d'école. On accroche ? Dimanche, à la fenêtre. Sarah souffle un peu sur le rond. Le papier ne bouge plus. Il est prêt. Le bleu a disparu. Tu as essuyé. Bravo. Une lueur passe sur le jaune. Tu vois le rayon ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1600,7 +1669,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1676,10 +1745,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Adam a nommé mercredi. Il a nommé samedi et dimanche. C'est le week-end.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah touche le papier du doigt.
+narrateur|Le jaune n'est plus collant.
+enfant-f|Samedi.
+enfant-f|Et dimanche.
+papa|Oui.
+papa|C'est le week-end.
+papa|Comme mercredi, pas d'école.
+enfant-f|On accroche ?
+papa|Dimanche, à la fenêtre.
+narrateur|Sarah souffle un peu sur le rond.
+narrateur|Le papier ne bouge plus.
+papa|Il est prêt.
+enfant-f|Le bleu a disparu.
+papa|Tu as essuyé.
+papa|Bravo.
+narrateur|Une lueur passe sur le jaune.
+papa|Tu vois le rayon ?
+enfant-f|Oui, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,12 +1789,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Adam range ses crayons. Papa prépare le goûter.</t>
+          <t>Dimanche, la vitre est froide. Papa tient le ruban. Le soleil va là. Contre le jour. Sarah plaque la feuille. Le ruban fait un petit bruit. Le jaune s'allume. Il chauffe un peu la pièce. C'est mon mercredi. Et le week-end le montre. Une tache pâle reste au bord. On voit encore le bleu. Un peu. On a essuyé ensemble. Merci, papa. Merci à toi. Le pot de bleu est vide, presque. Il brille encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam range ses crayons. Papa prépare le goûter.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Dimanche, la vitre est froide. Papa tient le ruban. Le soleil va là. Contre le jour. Sarah plaque la feuille. Le ruban fait un petit bruit. Le jaune s'allume. Il chauffe un peu la pièce. C'est mon mercredi. Et le week-end le montre. Une tache pâle reste au bord. On voit encore le bleu. Un peu. On a essuyé ensemble. Merci, papa. Merci à toi. Le pot de bleu est vide, presque. Il brille encore.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1772,7 +1857,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1840,10 +1925,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Adam range ses crayons. Papa prépare le goûter.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Dimanche, la vitre est froide.
+narrateur|Papa tient le ruban.
+enfant-f|Le soleil va là.
+papa|Contre le jour.
+narrateur|Sarah plaque la feuille.
+narrateur|Le ruban fait un petit bruit.
+narrateur|Le jaune s'allume.
+papa|Il chauffe un peu la pièce.
+enfant-f|C'est mon mercredi.
+papa|Et le week-end le montre.
+narrateur|Une tache pâle reste au bord.
+enfant-f|On voit encore le bleu.
+papa|Un peu.
+papa|On a essuyé ensemble.
+enfant-f|Merci, papa.
+papa|Merci à toi.
+narrateur|Le pot de bleu est vide, presque.
+narrateur|Il brille encore.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,12 +1969,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le soleil est à la fenêtre. Il va rester. Le jaune chauffe un peu la vitre. Ça sent encore la peinture, tout doux. Le rayon traverse le rond.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le soleil est à la fenêtre. Il va rester. Le jaune chauffe un peu la vitre. Ça sent encore la peinture, tout doux. Le rayon traverse le rond.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1929,14 +2030,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2008,10 +2109,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|Le soleil est à la fenêtre.
+papa|Il va rester.
+narrateur|Le jaune chauffe un peu la vitre.
+narrateur|Ça sent encore la peinture, tout doux.
+narrateur|Le rayon traverse le rond.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2172,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.002-01.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison</t>
+          <t>cuisine, table de peinture, mercredi puis week-end</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Adam, papa</t>
+          <t>Sarah, papa</t>
         </is>
       </c>
     </row>
